--- a/papers/P010/P010_工程复现问题清单_v1.xlsx
+++ b/papers/P010/P010_工程复现问题清单_v1.xlsx
@@ -30,13 +30,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF112A44"/>
+        <fgColor rgb="FF182D49"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0F4F9"/>
+        <fgColor rgb="FFF1F5F9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -55,13 +55,13 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment wrapText="1" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFill="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment wrapText="1" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -72,12 +72,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="25"/>
   <cols>
-    <col min="1" max="1" width="25" customWidth="1"/>
-    <col min="2" max="2" width="52" customWidth="1"/>
-    <col min="3" max="3" width="94" customWidth="1"/>
+    <col min="1" max="1" width="27" customWidth="1"/>
+    <col min="2" max="2" width="53" customWidth="1"/>
+    <col min="3" max="3" width="98" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -97,7 +97,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="80" customHeight="1">
+    <row r="2" ht="87" customHeight="1">
       <c r="A2" t="inlineStr" s="0">
         <is>
           <t xml:space="preserve">金融语义词表</t>
@@ -105,277 +105,226 @@
       </c>
       <c r="B2" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">这到底是什么？从哪里来，是行情数据吗？</t>
+          <t xml:space="preserve">词表是行情数据吗？怎么来，140条会一直固定吗？</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">不是行情数据或公式库，而是把研报、论文、书籍和研究经验中的市场机制抽象成可组合的概念条目，按五类存成JSON；真实OHLCV另供后续因子执行。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="80" customHeight="1">
+          <t xml:space="preserve">把金融论文、研报等知识整理成五类JSON“研究概念积木”，而非行情表或现成公式；OHLCV另供计算。单次在线搜索用当前词表，跨搜索周期可离线扩词。论文140条，当前仓库167条，版本不同。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="109" customHeight="1">
       <c r="A3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">词表是否固定</t>
+          <t xml:space="preserve">五维Plan与输入</t>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">140条是永远固定的吗？</t>
+          <t xml:space="preserve">五个维度是什么意思？Plan怎样进入LLM？</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">单次在线搜索在已启用词表内组合；不同搜索周期可离线补充词条。论文主实验140条，当前仓库启用167条，属于不同版本，不能直接混用。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="98" customHeight="1">
+          <t xml:space="preserve">Event事件、Context情境、Qualities确认条件、Direction走势方向、Output信号形式，共同构成尚未写公式的金融研究计划。程序将词表记录（ID/描述/适用范围等）展开成Prompt，由LLM再决定公式与参数。图解：https://github.com/epshoron/JXwork/blob/main/papers/P010/P010_SEMANTIC_PLAN_GUIDE.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="78" customHeight="1">
       <c r="A4" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">五维Plan的含义</t>
+          <t xml:space="preserve">大量Plan的生成</t>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Event、Context、Qualities、Direction、Output各做什么？</t>
+          <t xml:space="preserve">上万个Plan是LLM一个个想的吗？全部都执行？</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">依次规定发生什么事件、什么情境、附加确认条件、未来走势预期、输出信号形式。可理解为“量价突破＋VWAP附近＋过滤重复事件＋趋势延续＋衰减评分”，仍不是可执行代码。图解：https://github.com/epshoron/JXwork/blob/main/papers/P010/P010_SEMANTIC_PLAN_GUIDE.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="80" customHeight="1">
+          <t xml:space="preserve">程序从五类词表随机组合（Qualities可选0–3项），每轮先抽约10000个未评Plan，筛出16个才交给LLM写代码和真实评价，不是让LLM逐条想出并执行一万份。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="98" customHeight="1">
       <c r="A5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">条目与Prompt</t>
+          <t xml:space="preserve">搜索调度器</t>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一个语义记录长什么样，怎样交给LLM？</t>
+          <t xml:space="preserve">究竟谁决定先试哪些Plan？是Bandit吗？</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">每条JSON含ID、类型、作用范围、名称、金融描述、术语解释，不预设具体算子或窗口；程序将选中Plan涉及的记录展开后填入Code Agent的Prompt。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="80" customHeight="1">
+          <t xml:space="preserve">Python程序把16个实现名额分给三类：探索很少试过的语义组合、优先实现LightGBM预测高奖Plan、对已评高奖Plan局部变异。它不是P006的两臂Bandit。图解：https://github.com/epshoron/JXwork/blob/main/papers/P010/P010_SEMANTIC_PLAN_GUIDE.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="78" customHeight="1">
       <c r="A6" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">大量Plan的生成</t>
+          <t xml:space="preserve">探索新颖度</t>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">上万个Plan是LLM一个个想的吗？全部都执行？</t>
+          <t xml:space="preserve">怎样算某种语义组合还没有研究够？</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">Python从五类词表随机组合：除Qualities可选0–3项，其余各一项。每轮先抽约10000个候选，再去重和调度，仅选16个进入昂贵的代码实现与评价。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="110" customHeight="1">
+          <t xml:space="preserve">统计已试过的Event、Context及二者搭配次数，次数越少优先级越高；论文新颖度权重为搭配60%、Event25%、Context15%，不是LLM凭感觉判断新颖。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="87" customHeight="1">
       <c r="A7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">搜索调度器</t>
+          <t xml:space="preserve">预测奖励与经验学习</t>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">究竟谁决定先试哪些Plan？是Bandit吗？</t>
+          <t xml:space="preserve">没写代码的Plan怎么预测表现？真实结果怎样让它变准？</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">外部Python选择器给每轮16个实现名额分三路：优先未充分探索的组合、优先LightGBM预测奖励高的组合、对历史高分Plan作局部变异。它不是P006的Factor/Model双臂Bandit。图解：https://github.com/epshoron/JXwork/blob/main/papers/P010/P010_SEMANTIC_PLAN_GUIDE.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="80" customHeight="1">
+          <t xml:space="preserve">把已评价(Plan,真实Reward)中的语义ID、条件数和搭配编码成特征，训练外部LightGBM；当前代码用8个模型的预测均值为新Plan预估奖励，优先实现预测高分者。新实测Reward继续写缓存并重训评分器，**不微调生成LLM**。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="87" customHeight="1">
       <c r="A8" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">探索新颖度</t>
+          <t xml:space="preserve">真实Plan奖励</t>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">怎样算某种语义组合还没有研究够？</t>
+          <t xml:space="preserve">所谓Plan–Reward经验到底是什么？</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">统计已试过的Event、Context及二者搭配次数，次数越少优先级越高；论文新颖度权重为搭配60%、Event25%、Context15%，不是LLM凭感觉判断新颖。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="86" customHeight="1">
+          <t xml:space="preserve">一个Plan实现fast/slow两种因子尺度，分别计算10×RankIC＋RankICIR−2×信号时滞罚分，取较高奖励；失败且修复不成功记0。经验库保存**Plan与实测奖励**，不是只存LLM主观点评。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="109" customHeight="1">
       <c r="A9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">预测奖励</t>
+          <t xml:space="preserve">局部变异</t>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一个没写代码的Plan为什么会有预期分？</t>
+          <t xml:space="preserve">所谓树变异是什么？是在改AST代码树吗？</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LightGBM从历史(Plan,实测Reward)样本学习语义ID、类别搭配与条件数量对奖励的关联，再预测新Plan的可能评分；当前源码使用8个LightGBM回归器预测均值。预测值不是真实回测收益。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="86" customHeight="1">
+          <t xml:space="preserve">所谓“树变异”其实是**五维Plan局部编辑**：复制高奖Plan，替换Event/Context/Direction/Output，或增删/替换Quality，过滤重复后再让LLM实现。不是MCTS树或Python算子AST的子树交叉。图解：https://github.com/epshoron/JXwork/blob/main/papers/P010/P010_SEMANTIC_PLAN_GUIDE.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="87" customHeight="1">
       <c r="A10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">真实Plan奖励</t>
+          <t xml:space="preserve">LLM底座与职责</t>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">所谓Plan–Reward经验到底是什么？</t>
+          <t xml:space="preserve">Plan和因子是谁生成的，LLM在哪里参与？</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">一个Plan按fast/slow两个尺度实现后，用10×RankIC＋RankICIR－2×时滞敏感度计算奖励，取两尺度较高值；修复后仍执行失败则记0。缓存保存“具体Plan与真实得分”，供后来训练评分器。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="86" customHeight="1">
+          <t xml:space="preserve">Plan采样、排序、变异由Python完成；论文默认DeepSeek-V4-Flash Code Agent接收展开的Plan和数据接口要求，生成fast/slow Python因子。LLM写实现，不决定三路配额。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="78" customHeight="1">
       <c r="A11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">反馈和更新</t>
+          <t xml:space="preserve">质量检查与修复</t>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">实验结果怎样影响下一轮？会训练生成LLM吗？</t>
+          <t xml:space="preserve">生成因子后怎么知道可以用？</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">历史Plan–Reward持续写入累积Buffer，并重新训练外部LightGBM奖励预测器；下一轮它给未实现Plan估分。改变的是评分器、搜索选择和候选，不是生成LLM的神经网络权重。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="110" customHeight="1">
+          <t xml:space="preserve">执行程序检查接口、数值稳定和潜在未来信息；失败时可让LLM按报错修复一次，仍失败记0奖励。能运行不等于有预测效果。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="87" customHeight="1">
       <c r="A12" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">局部变异</t>
+          <t xml:space="preserve">因子池与下游预测</t>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">所谓树变异是什么？是在改AST代码树吗？</t>
+          <t xml:space="preserve">怎么留下因子？和P005池级边际贡献一样吗？</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">这里是对**五维Plan**做单步语义编辑：从已评高分Plan复制出新Plan，替换Event/Context/Direction/Output或增删/替换Quality；排除重复候选。不是P004的MCTS树扩展或P002的代码交叉。详解：https://github.com/epshoron/JXwork/blob/main/papers/P010/P010_SEMANTIC_PLAN_GUIDE.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="86" customHeight="1">
+          <t xml:space="preserve">P010按实测奖励排序，依次挑与已选因子绝对相关系数低于0.7的候选；不是P005逐个计算整池边际增益。另用下游LightGBM组合最终因子数值，再按Qlib Top50/Drop5回测。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="78" customHeight="1">
       <c r="A13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LLM底座与职责</t>
+          <t xml:space="preserve">搜索轮次与版本差异</t>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Plan和因子是谁生成的，LLM在哪里参与？</t>
+          <t xml:space="preserve">怎么分配探索名额，什么时候结束？</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Plan采样、排序与变异主要是Python程序；论文默认DeepSeek-V4-Flash负责接收选中Plan和数据契约，决定数学实现并生成Python因子（fast/slow两个时间尺度），并非负责搜索调度。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="80" customHeight="1">
+          <t xml:space="preserve">论文80轮×每轮16个，前10轮纯探索；论文以平滑下降公式调探索份额，但当前配置按历史数量分阶段设16/0/0→8/6/2→5/8/3→3/8/5，版本口径不能混同。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="98" customHeight="1">
       <c r="A14" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">质量检查与修复</t>
+          <t xml:space="preserve">源码与核验边界</t>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">生成因子后怎么知道可以用？</t>
+          <t xml:space="preserve">有没有真实源码，已复现了吗？</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="0">
         <is>
-          <t xml:space="preserve">程序核查可执行性、输入接口、数值稳定和前瞻信息；不合格只给LLM一次依据报错修复机会，仍失败的Plan按0奖励记入经验。代码能跑通不等于预测有效。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="86" customHeight="1">
-      <c r="A15" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">因子池与下游预测</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">怎么留下因子？和P005池级边际贡献一样吗？</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">P010按实测奖励排序，依次挑与已选因子绝对相关系数低于0.7的候选；不是P005逐个计算整池边际增益。另用下游LightGBM组合最终因子数值，再按Qlib Top50/Drop5回测。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="86" customHeight="1">
-      <c r="A16" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">搜索轮次与版本差异</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">怎么分配探索名额，什么时候结束？</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr" s="0">
-        <is>
-          <t xml:space="preserve">论文主实验80轮×每轮16个，前10轮纯探索；正文给出随历史评测数量平滑降低探索份额的方法。当前配置却是16/0/0→8/6/2→5/8/3→3/8/5的分段名额，不可未经核验说二者同一实现。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="98" customHeight="1">
-      <c r="A17" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">源码与核验边界</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">有没有真实源码，已复现了吗？</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr" s="2">
-        <is>
           <t xml:space="preserve">作者公开schema_space.py、selector.py、reward_model.py、workflow.py、JSON词表、Prompt和轻量demo；已静态核对部分代码与论文，但当前仓库词表和配额与主实验口径不同，尚未运行完整论文回测。源码：https://github.com/JingyangYi/AlphaSchema</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C17"/>
+  <autoFilter ref="A1:C14"/>
   <hyperlinks>
-    <hyperlink ref="C4" r:id="rId1" tooltip="打开详细解释或原始源码"/>
-    <hyperlink ref="C7" r:id="rId2" tooltip="打开详细解释或原始源码"/>
-    <hyperlink ref="C12" r:id="rId3" tooltip="打开详细解释或原始源码"/>
-    <hyperlink ref="C17" r:id="rId4" tooltip="打开详细解释或原始源码"/>
+    <hyperlink ref="C3" r:id="rId1" tooltip="打开论文、源码或机制图解"/>
+    <hyperlink ref="C5" r:id="rId2" tooltip="打开论文、源码或机制图解"/>
+    <hyperlink ref="C9" r:id="rId3" tooltip="打开论文、源码或机制图解"/>
+    <hyperlink ref="C14" r:id="rId4" tooltip="打开论文、源码或机制图解"/>
   </hyperlinks>
 </worksheet>
 </file>